--- a/checklist_forms/018_litigation_checklist_template--checklist_forms.xlsx
+++ b/checklist_forms/018_litigation_checklist_template--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'defendant'}</t>
+          <t>defendant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Defendant'}</t>
+          <t>Defendant</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'plaintiff'}</t>
+          <t>plaintiff</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Plaintiff'}</t>
+          <t>Plaintiff</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'defendant'}</t>
+          <t>defendant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Defendant'}</t>
+          <t>Defendant</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'plaintiff'}</t>
+          <t>plaintiff</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Plaintiff'}</t>
+          <t>Plaintiff</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'court_of_common_pleas'}</t>
+          <t>court_of_common_pleas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Court of Common Pleas'}</t>
+          <t>Court of Common Pleas</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'court_of_common_pleas_(small_claims)'}</t>
+          <t>court_of_common_pleas_(small_claims)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Court of Common Pleas (Small Claims)'}</t>
+          <t>Court of Common Pleas (Small Claims)</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'court_of_special_and_general_jurisdiction'}</t>
+          <t>court_of_special_and_general_jurisdiction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Court of Special and General Jurisdiction'}</t>
+          <t>Court of Special and General Jurisdiction</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'civil'}</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Civil'}</t>
+          <t>Civil</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'criminal'}</t>
+          <t>criminal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Criminal'}</t>
+          <t>Criminal</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'document_1'}</t>
+          <t>document_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Document 1'}</t>
+          <t>Document 1</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'document_2'}</t>
+          <t>document_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Document 2'}</t>
+          <t>Document 2</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'document_3'}</t>
+          <t>document_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Document 3'}</t>
+          <t>Document 3</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'document_4'}</t>
+          <t>document_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Document 4'}</t>
+          <t>Document 4</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'document_5'}</t>
+          <t>document_5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Document 5'}</t>
+          <t>Document 5</t>
         </is>
       </c>
     </row>
